--- a/src/data/downloads/2014_elections_of_municipal_authorities_by_election_20161030_sakrebulo_20140615_data_2026-04-30T16-20-00.xlsx
+++ b/src/data/downloads/2014_elections_of_municipal_authorities_by_election_20161030_sakrebulo_20140615_data_2026-04-30T16-20-00.xlsx
@@ -125,13 +125,13 @@
     <t>Archive</t>
   </si>
   <si>
-    <t>Comprehensive Election Data Archive of Georgia (CEDAG)</t>
+    <t>Georgia Election Data Archive (GEDA)</t>
   </si>
   <si>
     <t>Website</t>
   </si>
   <si>
-    <t>https://electionsdata.ge</t>
+    <t>https://electionsdata.ge/elections?type=local&amp;election=local_2014&amp;sub=local_2014_2016_oct30_sakrebulo_by_election</t>
   </si>
   <si>
     <t>Author</t>
@@ -158,12 +158,6 @@
     <t>local_2014</t>
   </si>
   <si>
-    <t>Sub-election ID</t>
-  </si>
-  <si>
-    <t>local_2014_2016_oct30_sakrebulo_by_election</t>
-  </si>
-  <si>
     <t>Election Type</t>
   </si>
   <si>
@@ -173,13 +167,13 @@
     <t>Election Date</t>
   </si>
   <si>
-    <t>2014-06-15</t>
+    <t>2016-10-30</t>
   </si>
   <si>
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-04-30T16:20:00.666Z</t>
+    <t>2026-04-30T18:50:28.616Z</t>
   </si>
   <si>
     <t>Data Source</t>
@@ -188,10 +182,16 @@
     <t>Public information requested from the Central Election Commission as part of the preparation of the National Democratic Institute's (NDI) election portal electionsdata.ge</t>
   </si>
   <si>
+    <t>Citation (APA)</t>
+  </si>
+  <si>
+    <t>Sichinava, D. (2026). Results of the 2014 elections of municipal authorities - October 30, 2016 Sakrebulo by-election. Georgia Election Data Archive (GEDA). https://electionsdata.ge/elections?type=local&amp;election=local_2014&amp;sub=local_2014_2016_oct30_sakrebulo_by_election</t>
+  </si>
+  <si>
     <t>License</t>
   </si>
   <si>
-    <t>Open data. Please cite CEDAG when using.</t>
+    <t>CC-BY-4.0</t>
   </si>
 </sst>
 </file>
@@ -1212,7 +1212,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2024,7 +2024,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2634,7 +2634,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3446,7 +3446,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
